--- a/yolo-seg__ANN/預測結果與評估指標_kfold_26n_mask幾何_長邊正規化_年齡_seed2.xlsx
+++ b/yolo-seg__ANN/預測結果與評估指標_kfold_26n_mask幾何_長邊正規化_年齡_seed2.xlsx
@@ -430,7 +430,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.42578125" customWidth="true"/>
+    <col min="6" max="6" width="13.7109375" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -489,28 +489,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>757.57460000000003</v>
+        <v>610.42669999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>21.003989007916328</v>
+        <v>20.117571875522362</v>
       </c>
       <c r="F2" s="0">
-        <v>-1.9960109920836722</v>
+        <v>-2.882428124477638</v>
       </c>
       <c r="G2" s="0">
-        <v>1.9960109920836722</v>
+        <v>2.882428124477638</v>
       </c>
       <c r="H2" s="0">
-        <v>20.503989007916328</v>
+        <v>19.617571875522362</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.4960109920836722</v>
+        <v>-3.382428124477638</v>
       </c>
       <c r="J2" s="0">
-        <v>2.4960109920836722</v>
+        <v>3.382428124477638</v>
       </c>
       <c r="K2" s="0">
         <v>5</v>
@@ -530,28 +530,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>491.95310000000001</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.280507401584622</v>
+        <v>20.464330929728497</v>
       </c>
       <c r="F3" s="0">
-        <v>0.28050740158462162</v>
+        <v>-0.53566907027150279</v>
       </c>
       <c r="G3" s="0">
-        <v>0.28050740158462162</v>
+        <v>0.53566907027150279</v>
       </c>
       <c r="H3" s="0">
-        <v>20.780507401584622</v>
+        <v>19.964330929728497</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.21949259841537838</v>
+        <v>-1.0356690702715028</v>
       </c>
       <c r="J3" s="0">
-        <v>0.21949259841537838</v>
+        <v>1.0356690702715028</v>
       </c>
       <c r="K3" s="0">
         <v>2</v>
@@ -571,28 +571,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>491.89060000000001</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.047839314817171</v>
+        <v>23.8973632264643</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.4521606851828288</v>
+        <v>0.39736322646430011</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4521606851828288</v>
+        <v>0.39736322646430011</v>
       </c>
       <c r="H4" s="0">
-        <v>20.547839314817171</v>
+        <v>23.3973632264643</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.9521606851828288</v>
+        <v>-0.10263677353569989</v>
       </c>
       <c r="J4" s="0">
-        <v>2.9521606851828288</v>
+        <v>0.10263677353569989</v>
       </c>
       <c r="K4" s="0">
         <v>4</v>
@@ -612,28 +612,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>491.41719999999998</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.992573764841183</v>
+        <v>19.601951630479665</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.0074262351588174624</v>
+        <v>-1.3980483695203354</v>
       </c>
       <c r="G5" s="0">
-        <v>0.0074262351588174624</v>
+        <v>1.3980483695203354</v>
       </c>
       <c r="H5" s="0">
-        <v>20.492573764841183</v>
+        <v>19.101951630479665</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.50742623515881746</v>
+        <v>-1.8980483695203354</v>
       </c>
       <c r="J5" s="0">
-        <v>0.50742623515881746</v>
+        <v>1.8980483695203354</v>
       </c>
       <c r="K5" s="0">
         <v>5</v>
@@ -653,28 +653,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>505.68939999999998</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.290499685708134</v>
+        <v>20.802192128563363</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.20950031429186566</v>
+        <v>-0.69780787143663758</v>
       </c>
       <c r="G6" s="0">
-        <v>0.20950031429186566</v>
+        <v>0.69780787143663758</v>
       </c>
       <c r="H6" s="0">
-        <v>20.790499685708134</v>
+        <v>20.302192128563363</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.70950031429186566</v>
+        <v>-1.1978078714366376</v>
       </c>
       <c r="J6" s="0">
-        <v>0.70950031429186566</v>
+        <v>1.1978078714366376</v>
       </c>
       <c r="K6" s="0">
         <v>2</v>
@@ -694,28 +694,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>494.42829999999998</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.000850186553578</v>
+        <v>22.586560035698398</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.99914981344642229</v>
+        <v>0.58656003569839754</v>
       </c>
       <c r="G7" s="0">
-        <v>0.99914981344642229</v>
+        <v>0.58656003569839754</v>
       </c>
       <c r="H7" s="0">
-        <v>20.500850186553578</v>
+        <v>22.086560035698398</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.4991498134464223</v>
+        <v>0.086560035698397542</v>
       </c>
       <c r="J7" s="0">
-        <v>1.4991498134464223</v>
+        <v>0.086560035698397542</v>
       </c>
       <c r="K7" s="0">
         <v>5</v>
@@ -735,28 +735,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>513.30700000000002</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.041719167008971</v>
+        <v>23.887883450789605</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.9582808329910293</v>
+        <v>-1.1121165492103948</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9582808329910293</v>
+        <v>1.1121165492103948</v>
       </c>
       <c r="H8" s="0">
-        <v>20.541719167008971</v>
+        <v>23.387883450789605</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.4582808329910293</v>
+        <v>-1.6121165492103948</v>
       </c>
       <c r="J8" s="0">
-        <v>4.4582808329910293</v>
+        <v>1.6121165492103948</v>
       </c>
       <c r="K8" s="0">
         <v>1</v>
@@ -776,28 +776,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>762.40570000000002</v>
+        <v>584.5915</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>21.168456244802602</v>
+        <v>19.720571282242663</v>
       </c>
       <c r="F9" s="0">
-        <v>0.66845624480260213</v>
+        <v>-0.77942871775733735</v>
       </c>
       <c r="G9" s="0">
-        <v>0.66845624480260213</v>
+        <v>0.77942871775733735</v>
       </c>
       <c r="H9" s="0">
-        <v>20.668456244802602</v>
+        <v>19.220571282242663</v>
       </c>
       <c r="I9" s="0">
-        <v>0.16845624480260213</v>
+        <v>-1.2794287177573374</v>
       </c>
       <c r="J9" s="0">
-        <v>0.16845624480260213</v>
+        <v>1.2794287177573374</v>
       </c>
       <c r="K9" s="0">
         <v>2</v>
@@ -817,28 +817,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>253.237</v>
+        <v>648.39279999999997</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.160759434203513</v>
+        <v>20.778904825919817</v>
       </c>
       <c r="F10" s="0">
-        <v>0.1607594342035128</v>
+        <v>-0.2210951740801832</v>
       </c>
       <c r="G10" s="0">
-        <v>0.1607594342035128</v>
+        <v>0.2210951740801832</v>
       </c>
       <c r="H10" s="0">
-        <v>20.660759434203513</v>
+        <v>20.278904825919817</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.3392405657964872</v>
+        <v>-0.7210951740801832</v>
       </c>
       <c r="J10" s="0">
-        <v>0.3392405657964872</v>
+        <v>0.7210951740801832</v>
       </c>
       <c r="K10" s="0">
         <v>2</v>
@@ -858,28 +858,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>705.75559999999996</v>
+        <v>466.6764</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>21.001514558913016</v>
+        <v>19.288300733498179</v>
       </c>
       <c r="F11" s="0">
-        <v>3.0015145589130157</v>
+        <v>1.2883007334981791</v>
       </c>
       <c r="G11" s="0">
-        <v>3.0015145589130157</v>
+        <v>1.2883007334981791</v>
       </c>
       <c r="H11" s="0">
-        <v>20.501514558913016</v>
+        <v>18.788300733498179</v>
       </c>
       <c r="I11" s="0">
-        <v>2.5015145589130157</v>
+        <v>0.78830073349817908</v>
       </c>
       <c r="J11" s="0">
-        <v>2.5015145589130157</v>
+        <v>0.78830073349817908</v>
       </c>
       <c r="K11" s="0">
         <v>5</v>
@@ -899,28 +899,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>493.79079999999999</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.884295731469138</v>
+        <v>23.984337003522985</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.1157042685308625</v>
+        <v>-1.0156629964770154</v>
       </c>
       <c r="G12" s="0">
-        <v>4.1157042685308625</v>
+        <v>1.0156629964770154</v>
       </c>
       <c r="H12" s="0">
-        <v>20.384295731469138</v>
+        <v>23.484337003522985</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.6157042685308625</v>
+        <v>-1.5156629964770154</v>
       </c>
       <c r="J12" s="0">
-        <v>4.6157042685308625</v>
+        <v>1.5156629964770154</v>
       </c>
       <c r="K12" s="0">
         <v>3</v>
@@ -940,28 +940,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>500.21780000000001</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.886088820329984</v>
+        <v>21.139201363369615</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.6139111796700156</v>
+        <v>-1.3607986366303848</v>
       </c>
       <c r="G13" s="0">
-        <v>1.6139111796700156</v>
+        <v>1.3607986366303848</v>
       </c>
       <c r="H13" s="0">
-        <v>20.386088820329984</v>
+        <v>20.639201363369615</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.1139111796700156</v>
+        <v>-1.8607986366303848</v>
       </c>
       <c r="J13" s="0">
-        <v>2.1139111796700156</v>
+        <v>1.8607986366303848</v>
       </c>
       <c r="K13" s="0">
         <v>3</v>
@@ -981,28 +981,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>497.86020000000002</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>20.9766723140221</v>
+        <v>21.101957898226829</v>
       </c>
       <c r="F14" s="0">
-        <v>0.47667231402209964</v>
+        <v>0.60195789822682855</v>
       </c>
       <c r="G14" s="0">
-        <v>0.47667231402209964</v>
+        <v>0.60195789822682855</v>
       </c>
       <c r="H14" s="0">
-        <v>20.4766723140221</v>
+        <v>20.601957898226829</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.023327685977900359</v>
+        <v>0.10195789822682855</v>
       </c>
       <c r="J14" s="0">
-        <v>0.023327685977900359</v>
+        <v>0.10195789822682855</v>
       </c>
       <c r="K14" s="0">
         <v>4</v>
@@ -1022,28 +1022,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>494.16919999999999</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.858827416389453</v>
+        <v>20.349036051988367</v>
       </c>
       <c r="F15" s="0">
-        <v>1.3588274163894525</v>
+        <v>0.84903605198836729</v>
       </c>
       <c r="G15" s="0">
-        <v>1.3588274163894525</v>
+        <v>0.84903605198836729</v>
       </c>
       <c r="H15" s="0">
-        <v>20.358827416389453</v>
+        <v>19.849036051988367</v>
       </c>
       <c r="I15" s="0">
-        <v>0.85882741638945248</v>
+        <v>0.34903605198836729</v>
       </c>
       <c r="J15" s="0">
-        <v>0.85882741638945248</v>
+        <v>0.34903605198836729</v>
       </c>
       <c r="K15" s="0">
         <v>3</v>
@@ -1063,28 +1063,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>481.47469999999999</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.270838399603299</v>
+        <v>20.560317179877288</v>
       </c>
       <c r="F16" s="0">
-        <v>1.7708383996032993</v>
+        <v>1.0603171798772877</v>
       </c>
       <c r="G16" s="0">
-        <v>1.7708383996032993</v>
+        <v>1.0603171798772877</v>
       </c>
       <c r="H16" s="0">
-        <v>20.770838399603299</v>
+        <v>20.060317179877288</v>
       </c>
       <c r="I16" s="0">
-        <v>1.2708383996032993</v>
+        <v>0.56031717987728769</v>
       </c>
       <c r="J16" s="0">
-        <v>1.2708383996032993</v>
+        <v>0.56031717987728769</v>
       </c>
       <c r="K16" s="0">
         <v>2</v>
@@ -1104,28 +1104,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>247.03380000000001</v>
+        <v>564.40920000000006</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>20.956774735217529</v>
+        <v>19.487786264527454</v>
       </c>
       <c r="F17" s="0">
-        <v>2.4567747352175289</v>
+        <v>0.98778626452745399</v>
       </c>
       <c r="G17" s="0">
-        <v>2.4567747352175289</v>
+        <v>0.98778626452745399</v>
       </c>
       <c r="H17" s="0">
-        <v>20.456774735217529</v>
+        <v>18.987786264527454</v>
       </c>
       <c r="I17" s="0">
-        <v>1.9567747352175289</v>
+        <v>0.487786264527454</v>
       </c>
       <c r="J17" s="0">
-        <v>1.9567747352175289</v>
+        <v>0.487786264527454</v>
       </c>
       <c r="K17" s="0">
         <v>4</v>
@@ -1145,28 +1145,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>250.61840000000001</v>
+        <v>736.66660000000002</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.818627637764763</v>
+        <v>23.615705050608518</v>
       </c>
       <c r="F18" s="0">
-        <v>-2.931372362235237</v>
+        <v>-0.13429494939148157</v>
       </c>
       <c r="G18" s="0">
-        <v>2.931372362235237</v>
+        <v>0.13429494939148157</v>
       </c>
       <c r="H18" s="0">
-        <v>20.318627637764763</v>
+        <v>23.115705050608518</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.431372362235237</v>
+        <v>-0.63429494939148157</v>
       </c>
       <c r="J18" s="0">
-        <v>3.431372362235237</v>
+        <v>0.63429494939148157</v>
       </c>
       <c r="K18" s="0">
         <v>3</v>
@@ -1186,28 +1186,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>503.90179999999998</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.012877079728643</v>
+        <v>21.124803943722192</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2371229202713572</v>
+        <v>-1.1251960562778081</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2371229202713572</v>
+        <v>1.1251960562778081</v>
       </c>
       <c r="H19" s="0">
-        <v>20.512877079728643</v>
+        <v>20.624803943722192</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7371229202713572</v>
+        <v>-1.6251960562778081</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7371229202713572</v>
+        <v>1.6251960562778081</v>
       </c>
       <c r="K19" s="0">
         <v>1</v>
@@ -1227,28 +1227,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>504.19889999999998</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.000725846263592</v>
+        <v>23.691781206854046</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.4992741537364083</v>
+        <v>-1.8082187931459544</v>
       </c>
       <c r="G20" s="0">
-        <v>4.4992741537364083</v>
+        <v>1.8082187931459544</v>
       </c>
       <c r="H20" s="0">
-        <v>20.500725846263592</v>
+        <v>23.191781206854046</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.9992741537364083</v>
+        <v>-2.3082187931459544</v>
       </c>
       <c r="J20" s="0">
-        <v>4.9992741537364083</v>
+        <v>2.3082187931459544</v>
       </c>
       <c r="K20" s="0">
         <v>5</v>
@@ -1268,28 +1268,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>750.87540000000001</v>
+        <v>533.39049999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.968098399670961</v>
+        <v>18.533588534080639</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.5319016003290393</v>
+        <v>-3.9664114659193608</v>
       </c>
       <c r="G21" s="0">
-        <v>1.5319016003290393</v>
+        <v>3.9664114659193608</v>
       </c>
       <c r="H21" s="0">
-        <v>20.468098399670961</v>
+        <v>18.033588534080639</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.0319016003290393</v>
+        <v>-4.4664114659193608</v>
       </c>
       <c r="J21" s="0">
-        <v>2.0319016003290393</v>
+        <v>4.4664114659193608</v>
       </c>
       <c r="K21" s="0">
         <v>3</v>
@@ -1309,28 +1309,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>507.5804</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.981005143367884</v>
+        <v>20.081363478276934</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.51899485663211564</v>
+        <v>-1.4186365217230659</v>
       </c>
       <c r="G22" s="0">
-        <v>0.51899485663211564</v>
+        <v>1.4186365217230659</v>
       </c>
       <c r="H22" s="0">
-        <v>20.481005143367884</v>
+        <v>19.581363478276934</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.0189948566321157</v>
+        <v>-1.9186365217230659</v>
       </c>
       <c r="J22" s="0">
-        <v>1.0189948566321157</v>
+        <v>1.9186365217230659</v>
       </c>
       <c r="K22" s="0">
         <v>4</v>
@@ -1350,28 +1350,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>498.38549999999998</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.03262114338354</v>
+        <v>21.631161031579019</v>
       </c>
       <c r="F23" s="0">
-        <v>1.0326211433835404</v>
+        <v>1.631161031579019</v>
       </c>
       <c r="G23" s="0">
-        <v>1.0326211433835404</v>
+        <v>1.631161031579019</v>
       </c>
       <c r="H23" s="0">
-        <v>20.53262114338354</v>
+        <v>21.131161031579019</v>
       </c>
       <c r="I23" s="0">
-        <v>0.53262114338354039</v>
+        <v>1.131161031579019</v>
       </c>
       <c r="J23" s="0">
-        <v>0.53262114338354039</v>
+        <v>1.131161031579019</v>
       </c>
       <c r="K23" s="0">
         <v>4</v>
@@ -1391,28 +1391,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>487.82440000000003</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.242861395286067</v>
+        <v>19.805353319548615</v>
       </c>
       <c r="F24" s="0">
-        <v>1.7428613952860665</v>
+        <v>0.30535331954861533</v>
       </c>
       <c r="G24" s="0">
-        <v>1.7428613952860665</v>
+        <v>0.30535331954861533</v>
       </c>
       <c r="H24" s="0">
-        <v>20.742861395286067</v>
+        <v>19.305353319548615</v>
       </c>
       <c r="I24" s="0">
-        <v>1.2428613952860665</v>
+        <v>-0.19464668045138467</v>
       </c>
       <c r="J24" s="0">
-        <v>1.2428613952860665</v>
+        <v>0.19464668045138467</v>
       </c>
       <c r="K24" s="0">
         <v>2</v>
@@ -1432,28 +1432,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>497.21030000000002</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.032132375313598</v>
+        <v>19.891421627213376</v>
       </c>
       <c r="F25" s="0">
-        <v>2.5321323753135978</v>
+        <v>1.3914216272133757</v>
       </c>
       <c r="G25" s="0">
-        <v>2.5321323753135978</v>
+        <v>1.3914216272133757</v>
       </c>
       <c r="H25" s="0">
-        <v>20.532132375313598</v>
+        <v>19.391421627213376</v>
       </c>
       <c r="I25" s="0">
-        <v>2.0321323753135978</v>
+        <v>0.8914216272133757</v>
       </c>
       <c r="J25" s="0">
-        <v>2.0321323753135978</v>
+        <v>0.8914216272133757</v>
       </c>
       <c r="K25" s="0">
         <v>1</v>
@@ -1473,28 +1473,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>501.99489999999997</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.901225162976317</v>
+        <v>22.265019204983613</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.34877483702368295</v>
+        <v>1.0150192049836129</v>
       </c>
       <c r="G26" s="0">
-        <v>0.34877483702368295</v>
+        <v>1.0150192049836129</v>
       </c>
       <c r="H26" s="0">
-        <v>20.401225162976317</v>
+        <v>21.765019204983613</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.84877483702368295</v>
+        <v>0.51501920498361287</v>
       </c>
       <c r="J26" s="0">
-        <v>0.84877483702368295</v>
+        <v>0.51501920498361287</v>
       </c>
       <c r="K26" s="0">
         <v>3</v>
@@ -1514,28 +1514,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>494.10910000000001</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.004051326201058</v>
+        <v>20.745992752984368</v>
       </c>
       <c r="F27" s="0">
-        <v>1.7540513262010577</v>
+        <v>1.4959927529843675</v>
       </c>
       <c r="G27" s="0">
-        <v>1.7540513262010577</v>
+        <v>1.4959927529843675</v>
       </c>
       <c r="H27" s="0">
-        <v>20.504051326201058</v>
+        <v>20.245992752984368</v>
       </c>
       <c r="I27" s="0">
-        <v>1.2540513262010578</v>
+        <v>0.99599275298436751</v>
       </c>
       <c r="J27" s="0">
-        <v>1.2540513262010578</v>
+        <v>0.99599275298436751</v>
       </c>
       <c r="K27" s="0">
         <v>4</v>
@@ -1555,28 +1555,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>511.18400000000003</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>20.997241324047394</v>
+        <v>22.00611947989659</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.75275867595260593</v>
+        <v>0.25611947989659001</v>
       </c>
       <c r="G28" s="0">
-        <v>0.75275867595260593</v>
+        <v>0.25611947989659001</v>
       </c>
       <c r="H28" s="0">
-        <v>20.497241324047394</v>
+        <v>21.50611947989659</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.2527586759526059</v>
+        <v>-0.24388052010340999</v>
       </c>
       <c r="J28" s="0">
-        <v>1.2527586759526059</v>
+        <v>0.24388052010340999</v>
       </c>
       <c r="K28" s="0">
         <v>5</v>
@@ -1596,28 +1596,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>734.76130000000001</v>
+        <v>527.93060000000003</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.022589741271887</v>
+        <v>19.1410482872183</v>
       </c>
       <c r="F29" s="0">
-        <v>0.27258974127188651</v>
+        <v>-1.6089517127816997</v>
       </c>
       <c r="G29" s="0">
-        <v>0.27258974127188651</v>
+        <v>1.6089517127816997</v>
       </c>
       <c r="H29" s="0">
-        <v>20.522589741271887</v>
+        <v>18.6410482872183</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.22741025872811349</v>
+        <v>-2.1089517127816997</v>
       </c>
       <c r="J29" s="0">
-        <v>0.22741025872811349</v>
+        <v>2.1089517127816997</v>
       </c>
       <c r="K29" s="0">
         <v>4</v>
@@ -1637,28 +1637,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>502.2962</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.198442923395305</v>
+        <v>21.815703823855085</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.30155707660469489</v>
+        <v>0.31570382385508467</v>
       </c>
       <c r="G30" s="0">
-        <v>0.30155707660469489</v>
+        <v>0.31570382385508467</v>
       </c>
       <c r="H30" s="0">
-        <v>20.698442923395305</v>
+        <v>21.315703823855085</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.80155707660469489</v>
+        <v>-0.18429617614491534</v>
       </c>
       <c r="J30" s="0">
-        <v>0.80155707660469489</v>
+        <v>0.18429617614491534</v>
       </c>
       <c r="K30" s="0">
         <v>2</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>256.38499999999999</v>
+        <v>687.38679999999999</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.227090271411701</v>
+        <v>22.044979385720652</v>
       </c>
       <c r="F31" s="0">
-        <v>1.7270902714117007</v>
+        <v>2.5449793857206515</v>
       </c>
       <c r="G31" s="0">
-        <v>1.7270902714117007</v>
+        <v>2.5449793857206515</v>
       </c>
       <c r="H31" s="0">
-        <v>20.727090271411701</v>
+        <v>21.544979385720652</v>
       </c>
       <c r="I31" s="0">
-        <v>1.2270902714117007</v>
+        <v>2.0449793857206515</v>
       </c>
       <c r="J31" s="0">
-        <v>1.2270902714117007</v>
+        <v>2.0449793857206515</v>
       </c>
       <c r="K31" s="0">
         <v>2</v>
@@ -1719,28 +1719,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>252.7089</v>
+        <v>664.20730000000003</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.226702828149318</v>
+        <v>21.409987802133205</v>
       </c>
       <c r="F32" s="0">
-        <v>1.7267028281493175</v>
+        <v>1.9099878021332053</v>
       </c>
       <c r="G32" s="0">
-        <v>1.7267028281493175</v>
+        <v>1.9099878021332053</v>
       </c>
       <c r="H32" s="0">
-        <v>20.726702828149318</v>
+        <v>20.909987802133205</v>
       </c>
       <c r="I32" s="0">
-        <v>1.2267028281493175</v>
+        <v>1.4099878021332053</v>
       </c>
       <c r="J32" s="0">
-        <v>1.2267028281493175</v>
+        <v>1.4099878021332053</v>
       </c>
       <c r="K32" s="0">
         <v>2</v>
@@ -1760,28 +1760,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>251.91499999999999</v>
+        <v>700.82140000000004</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>20.980678859432679</v>
+        <v>21.493226120445865</v>
       </c>
       <c r="F33" s="0">
-        <v>-0.019321140567321038</v>
+        <v>0.49322612044586478</v>
       </c>
       <c r="G33" s="0">
-        <v>0.019321140567321038</v>
+        <v>0.49322612044586478</v>
       </c>
       <c r="H33" s="0">
-        <v>20.480678859432679</v>
+        <v>20.993226120445865</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.51932114056732104</v>
+        <v>-0.0067738795541352204</v>
       </c>
       <c r="J33" s="0">
-        <v>0.51932114056732104</v>
+        <v>0.0067738795541352204</v>
       </c>
       <c r="K33" s="0">
         <v>1</v>
@@ -1801,28 +1801,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>499.10570000000001</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.872358397379838</v>
+        <v>20.338252438811395</v>
       </c>
       <c r="F34" s="0">
-        <v>0.62235839737983767</v>
+        <v>0.088252438811394995</v>
       </c>
       <c r="G34" s="0">
-        <v>0.62235839737983767</v>
+        <v>0.088252438811394995</v>
       </c>
       <c r="H34" s="0">
-        <v>20.372358397379838</v>
+        <v>19.838252438811395</v>
       </c>
       <c r="I34" s="0">
-        <v>0.12235839737983767</v>
+        <v>-0.411747561188605</v>
       </c>
       <c r="J34" s="0">
-        <v>0.12235839737983767</v>
+        <v>0.411747561188605</v>
       </c>
       <c r="K34" s="0">
         <v>3</v>
@@ -1842,28 +1842,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>500.55090000000001</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.026148310179252</v>
+        <v>20.301393945553283</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.47385168982074788</v>
+        <v>-1.1986060544467172</v>
       </c>
       <c r="G35" s="0">
-        <v>0.47385168982074788</v>
+        <v>1.1986060544467172</v>
       </c>
       <c r="H35" s="0">
-        <v>20.526148310179252</v>
+        <v>19.801393945553283</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.97385168982074788</v>
+        <v>-1.6986060544467172</v>
       </c>
       <c r="J35" s="0">
-        <v>0.97385168982074788</v>
+        <v>1.6986060544467172</v>
       </c>
       <c r="K35" s="0">
         <v>1</v>
@@ -1883,28 +1883,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>492.50330000000002</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.025516769977195</v>
+        <v>20.001641507845868</v>
       </c>
       <c r="F36" s="0">
-        <v>1.5255167699771946</v>
+        <v>0.50164150784586781</v>
       </c>
       <c r="G36" s="0">
-        <v>1.5255167699771946</v>
+        <v>0.50164150784586781</v>
       </c>
       <c r="H36" s="0">
-        <v>20.525516769977195</v>
+        <v>19.501641507845868</v>
       </c>
       <c r="I36" s="0">
-        <v>1.0255167699771946</v>
+        <v>0.0016415078458678067</v>
       </c>
       <c r="J36" s="0">
-        <v>1.0255167699771946</v>
+        <v>0.0016415078458678067</v>
       </c>
       <c r="K36" s="0">
         <v>1</v>
@@ -1924,28 +1924,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>493.493</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>21.011319938833491</v>
+        <v>22.885844580639684</v>
       </c>
       <c r="F37" s="0">
-        <v>-3.9886800611665088</v>
+        <v>-2.1141554193603156</v>
       </c>
       <c r="G37" s="0">
-        <v>3.9886800611665088</v>
+        <v>2.1141554193603156</v>
       </c>
       <c r="H37" s="0">
-        <v>20.511319938833491</v>
+        <v>22.385844580639684</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.4886800611665088</v>
+        <v>-2.6141554193603156</v>
       </c>
       <c r="J37" s="0">
-        <v>4.4886800611665088</v>
+        <v>2.6141554193603156</v>
       </c>
       <c r="K37" s="0">
         <v>4</v>
@@ -1965,28 +1965,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>497.25240000000002</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.997172730925609</v>
+        <v>19.823956686981021</v>
       </c>
       <c r="F38" s="0">
-        <v>1.9971727309256089</v>
+        <v>0.82395668698102043</v>
       </c>
       <c r="G38" s="0">
-        <v>1.9971727309256089</v>
+        <v>0.82395668698102043</v>
       </c>
       <c r="H38" s="0">
-        <v>20.497172730925609</v>
+        <v>19.323956686981021</v>
       </c>
       <c r="I38" s="0">
-        <v>1.4971727309256089</v>
+        <v>0.32395668698102043</v>
       </c>
       <c r="J38" s="0">
-        <v>1.4971727309256089</v>
+        <v>0.32395668698102043</v>
       </c>
       <c r="K38" s="0">
         <v>5</v>
@@ -2006,28 +2006,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>507.44290000000001</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.865778105791527</v>
+        <v>20.398639707450201</v>
       </c>
       <c r="F39" s="0">
-        <v>1.8657781057915273</v>
+        <v>1.3986397074502008</v>
       </c>
       <c r="G39" s="0">
-        <v>1.8657781057915273</v>
+        <v>1.3986397074502008</v>
       </c>
       <c r="H39" s="0">
-        <v>20.365778105791527</v>
+        <v>19.898639707450201</v>
       </c>
       <c r="I39" s="0">
-        <v>1.3657781057915273</v>
+        <v>0.89863970745020083</v>
       </c>
       <c r="J39" s="0">
-        <v>1.3657781057915273</v>
+        <v>0.89863970745020083</v>
       </c>
       <c r="K39" s="0">
         <v>3</v>
@@ -2047,28 +2047,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>330.94639999999998</v>
+        <v>762.38530000000003</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.11474537979802</v>
+        <v>23.601386109442707</v>
       </c>
       <c r="F40" s="0">
-        <v>0.1147453797980198</v>
+        <v>2.6013861094427071</v>
       </c>
       <c r="G40" s="0">
-        <v>0.1147453797980198</v>
+        <v>2.6013861094427071</v>
       </c>
       <c r="H40" s="0">
-        <v>20.61474537979802</v>
+        <v>23.101386109442707</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.3852546202019802</v>
+        <v>2.1013861094427071</v>
       </c>
       <c r="J40" s="0">
-        <v>0.3852546202019802</v>
+        <v>2.1013861094427071</v>
       </c>
       <c r="K40" s="0">
         <v>2</v>
@@ -2088,28 +2088,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>495.67720000000003</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.171923708318072</v>
+        <v>21.273364363283349</v>
       </c>
       <c r="F41" s="0">
-        <v>0.67192370831807224</v>
+        <v>0.77336436328334912</v>
       </c>
       <c r="G41" s="0">
-        <v>0.67192370831807224</v>
+        <v>0.77336436328334912</v>
       </c>
       <c r="H41" s="0">
-        <v>20.671923708318072</v>
+        <v>20.773364363283349</v>
       </c>
       <c r="I41" s="0">
-        <v>0.17192370831807224</v>
+        <v>0.27336436328334912</v>
       </c>
       <c r="J41" s="0">
-        <v>0.17192370831807224</v>
+        <v>0.27336436328334912</v>
       </c>
       <c r="K41" s="0">
         <v>2</v>
@@ -2129,28 +2129,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>748.70209999999997</v>
+        <v>523.23350000000005</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.061290440385886</v>
+        <v>19.090539729661465</v>
       </c>
       <c r="F42" s="0">
-        <v>1.8112904403858856</v>
+        <v>-0.15946027033853483</v>
       </c>
       <c r="G42" s="0">
-        <v>1.8112904403858856</v>
+        <v>0.15946027033853483</v>
       </c>
       <c r="H42" s="0">
-        <v>20.561290440385886</v>
+        <v>18.590539729661465</v>
       </c>
       <c r="I42" s="0">
-        <v>1.3112904403858856</v>
+        <v>-0.65946027033853483</v>
       </c>
       <c r="J42" s="0">
-        <v>1.3112904403858856</v>
+        <v>0.65946027033853483</v>
       </c>
       <c r="K42" s="0">
         <v>4</v>
@@ -2170,28 +2170,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>494.75599999999997</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.993020274240447</v>
+        <v>19.629735863092161</v>
       </c>
       <c r="F43" s="0">
-        <v>0.99302027424044681</v>
+        <v>-0.37026413690783855</v>
       </c>
       <c r="G43" s="0">
-        <v>0.99302027424044681</v>
+        <v>0.37026413690783855</v>
       </c>
       <c r="H43" s="0">
-        <v>20.493020274240447</v>
+        <v>19.129735863092161</v>
       </c>
       <c r="I43" s="0">
-        <v>0.49302027424044681</v>
+        <v>-0.87026413690783855</v>
       </c>
       <c r="J43" s="0">
-        <v>0.49302027424044681</v>
+        <v>0.87026413690783855</v>
       </c>
       <c r="K43" s="0">
         <v>5</v>
@@ -2211,28 +2211,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>494.714</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.875599941181999</v>
+        <v>20.962302862798499</v>
       </c>
       <c r="F44" s="0">
-        <v>0.87559994118199924</v>
+        <v>0.96230286279849864</v>
       </c>
       <c r="G44" s="0">
-        <v>0.87559994118199924</v>
+        <v>0.96230286279849864</v>
       </c>
       <c r="H44" s="0">
-        <v>20.375599941181999</v>
+        <v>20.462302862798499</v>
       </c>
       <c r="I44" s="0">
-        <v>0.37559994118199924</v>
+        <v>0.46230286279849864</v>
       </c>
       <c r="J44" s="0">
-        <v>0.37559994118199924</v>
+        <v>0.46230286279849864</v>
       </c>
       <c r="K44" s="0">
         <v>3</v>
@@ -2252,28 +2252,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>497.33580000000001</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.029019288752956</v>
+        <v>19.847229478702079</v>
       </c>
       <c r="F45" s="0">
-        <v>1.0290192887529557</v>
+        <v>-0.15277052129792068</v>
       </c>
       <c r="G45" s="0">
-        <v>1.0290192887529557</v>
+        <v>0.15277052129792068</v>
       </c>
       <c r="H45" s="0">
-        <v>20.529019288752956</v>
+        <v>19.347229478702079</v>
       </c>
       <c r="I45" s="0">
-        <v>0.52901928875295567</v>
+        <v>-0.65277052129792068</v>
       </c>
       <c r="J45" s="0">
-        <v>0.52901928875295567</v>
+        <v>0.65277052129792068</v>
       </c>
       <c r="K45" s="0">
         <v>1</v>
@@ -2293,28 +2293,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>254.3287</v>
+        <v>725.4751</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.835356255012986</v>
+        <v>23.714954897495979</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.1646437449870142</v>
+        <v>1.7149548974959785</v>
       </c>
       <c r="G46" s="0">
-        <v>1.1646437449870142</v>
+        <v>1.7149548974959785</v>
       </c>
       <c r="H46" s="0">
-        <v>20.335356255012986</v>
+        <v>23.214954897495979</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.6646437449870142</v>
+        <v>1.2149548974959785</v>
       </c>
       <c r="J46" s="0">
-        <v>1.6646437449870142</v>
+        <v>1.2149548974959785</v>
       </c>
       <c r="K46" s="0">
         <v>3</v>
@@ -2334,28 +2334,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>247.4494</v>
+        <v>700.72990000000004</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.833533446180724</v>
+        <v>22.493454106758119</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.1664665538192765</v>
+        <v>0.49345410675811863</v>
       </c>
       <c r="G47" s="0">
-        <v>1.1664665538192765</v>
+        <v>0.49345410675811863</v>
       </c>
       <c r="H47" s="0">
-        <v>20.333533446180724</v>
+        <v>21.993454106758119</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.6664665538192765</v>
+        <v>-0.0065458932418813731</v>
       </c>
       <c r="J47" s="0">
-        <v>1.6664665538192765</v>
+        <v>0.0065458932418813731</v>
       </c>
       <c r="K47" s="0">
         <v>3</v>
@@ -2375,28 +2375,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>243.8894</v>
+        <v>697.40779999999995</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.00809164029533</v>
+        <v>21.840840602271516</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.9919083597046701</v>
+        <v>-1.1591593977284838</v>
       </c>
       <c r="G48" s="0">
-        <v>1.9919083597046701</v>
+        <v>1.1591593977284838</v>
       </c>
       <c r="H48" s="0">
-        <v>20.50809164029533</v>
+        <v>21.340840602271516</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.4919083597046701</v>
+        <v>-1.6591593977284838</v>
       </c>
       <c r="J48" s="0">
-        <v>2.4919083597046701</v>
+        <v>1.6591593977284838</v>
       </c>
       <c r="K48" s="0">
         <v>1</v>
@@ -2416,28 +2416,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>246.52959999999999</v>
+        <v>664.56500000000005</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.997899042053387</v>
+        <v>20.943701362253084</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.75210095794661314</v>
+        <v>-0.80629863774691657</v>
       </c>
       <c r="G49" s="0">
-        <v>0.75210095794661314</v>
+        <v>0.80629863774691657</v>
       </c>
       <c r="H49" s="0">
-        <v>20.497899042053387</v>
+        <v>20.443701362253084</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.2521009579466131</v>
+        <v>-1.3062986377469166</v>
       </c>
       <c r="J49" s="0">
-        <v>1.2521009579466131</v>
+        <v>1.3062986377469166</v>
       </c>
       <c r="K49" s="0">
         <v>1</v>
@@ -2457,28 +2457,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>253.74959999999999</v>
+        <v>689.15930000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>20.993387436356205</v>
+        <v>21.548713042527616</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.50661256364379526</v>
+        <v>0.048713042527616324</v>
       </c>
       <c r="G50" s="0">
-        <v>0.50661256364379526</v>
+        <v>0.048713042527616324</v>
       </c>
       <c r="H50" s="0">
-        <v>20.493387436356205</v>
+        <v>21.048713042527616</v>
       </c>
       <c r="I50" s="0">
-        <v>-1.0066125636437953</v>
+        <v>-0.45128695747238368</v>
       </c>
       <c r="J50" s="0">
-        <v>1.0066125636437953</v>
+        <v>0.45128695747238368</v>
       </c>
       <c r="K50" s="0">
         <v>5</v>
@@ -2498,28 +2498,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>245.00049999999999</v>
+        <v>610.64480000000003</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.177081787965353</v>
+        <v>20.129063444935426</v>
       </c>
       <c r="F51" s="0">
-        <v>1.9770817879653535</v>
+        <v>0.92906344493542647</v>
       </c>
       <c r="G51" s="0">
-        <v>1.9770817879653535</v>
+        <v>0.92906344493542647</v>
       </c>
       <c r="H51" s="0">
-        <v>20.677081787965353</v>
+        <v>19.629063444935426</v>
       </c>
       <c r="I51" s="0">
-        <v>1.4770817879653535</v>
+        <v>0.42906344493542648</v>
       </c>
       <c r="J51" s="0">
-        <v>1.4770817879653535</v>
+        <v>0.42906344493542648</v>
       </c>
       <c r="K51" s="0">
         <v>2</v>
@@ -2539,28 +2539,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>249.13220000000001</v>
+        <v>576.71630000000005</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>20.998102918886485</v>
+        <v>19.77873962081226</v>
       </c>
       <c r="F52" s="0">
-        <v>3.4981029188864845</v>
+        <v>2.2787396208122601</v>
       </c>
       <c r="G52" s="0">
-        <v>3.4981029188864845</v>
+        <v>2.2787396208122601</v>
       </c>
       <c r="H52" s="0">
-        <v>20.498102918886485</v>
+        <v>19.27873962081226</v>
       </c>
       <c r="I52" s="0">
-        <v>2.9981029188864845</v>
+        <v>1.7787396208122601</v>
       </c>
       <c r="J52" s="0">
-        <v>2.9981029188864845</v>
+        <v>1.7787396208122601</v>
       </c>
       <c r="K52" s="0">
         <v>1</v>
@@ -2580,28 +2580,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>248.1223</v>
+        <v>598.05470000000003</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>20.967162733299407</v>
+        <v>19.947002364420335</v>
       </c>
       <c r="F53" s="0">
-        <v>2.5671627332994085</v>
+        <v>1.5470023644203366</v>
       </c>
       <c r="G53" s="0">
-        <v>2.5671627332994085</v>
+        <v>1.5470023644203366</v>
       </c>
       <c r="H53" s="0">
-        <v>20.467162733299407</v>
+        <v>19.447002364420335</v>
       </c>
       <c r="I53" s="0">
-        <v>2.0671627332994085</v>
+        <v>1.0470023644203366</v>
       </c>
       <c r="J53" s="0">
-        <v>2.0671627332994085</v>
+        <v>1.0470023644203366</v>
       </c>
       <c r="K53" s="0">
         <v>4</v>
@@ -2621,28 +2621,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>246.3682</v>
+        <v>573.06939999999997</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>20.993280761513695</v>
+        <v>19.625533753311757</v>
       </c>
       <c r="F54" s="0">
-        <v>1.9932807615136952</v>
+        <v>0.62553375331175687</v>
       </c>
       <c r="G54" s="0">
-        <v>1.9932807615136952</v>
+        <v>0.62553375331175687</v>
       </c>
       <c r="H54" s="0">
-        <v>20.493280761513695</v>
+        <v>19.125533753311757</v>
       </c>
       <c r="I54" s="0">
-        <v>1.4932807615136952</v>
+        <v>0.12553375331175687</v>
       </c>
       <c r="J54" s="0">
-        <v>1.4932807615136952</v>
+        <v>0.12553375331175687</v>
       </c>
       <c r="K54" s="0">
         <v>5</v>
@@ -2662,28 +2662,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>503.7901</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>21.000188798165784</v>
+        <v>20.114772213833486</v>
       </c>
       <c r="F55" s="0">
-        <v>1.5001887981657838</v>
+        <v>0.61477221383348635</v>
       </c>
       <c r="G55" s="0">
-        <v>1.5001887981657838</v>
+        <v>0.61477221383348635</v>
       </c>
       <c r="H55" s="0">
-        <v>20.500188798165784</v>
+        <v>19.614772213833486</v>
       </c>
       <c r="I55" s="0">
-        <v>1.0001887981657838</v>
+        <v>0.11477221383348635</v>
       </c>
       <c r="J55" s="0">
-        <v>1.0001887981657838</v>
+        <v>0.11477221383348635</v>
       </c>
       <c r="K55" s="0">
         <v>5</v>
@@ -2703,28 +2703,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>514.5693</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.922807057192614</v>
+        <v>21.956468192337773</v>
       </c>
       <c r="F56" s="0">
-        <v>0.42280705719261391</v>
+        <v>1.4564681923377734</v>
       </c>
       <c r="G56" s="0">
-        <v>0.42280705719261391</v>
+        <v>1.4564681923377734</v>
       </c>
       <c r="H56" s="0">
-        <v>20.422807057192614</v>
+        <v>21.456468192337773</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.077192942807386089</v>
+        <v>0.95646819233777336</v>
       </c>
       <c r="J56" s="0">
-        <v>0.077192942807386089</v>
+        <v>0.95646819233777336</v>
       </c>
       <c r="K56" s="0">
         <v>3</v>
@@ -2744,28 +2744,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>488.1463</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.010600245994489</v>
+        <v>20.575523939993058</v>
       </c>
       <c r="F57" s="0">
-        <v>0.010600245994488944</v>
+        <v>-0.42447606000694194</v>
       </c>
       <c r="G57" s="0">
-        <v>0.010600245994488944</v>
+        <v>0.42447606000694194</v>
       </c>
       <c r="H57" s="0">
-        <v>20.510600245994489</v>
+        <v>20.075523939993058</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.48939975400551106</v>
+        <v>-0.92447606000694194</v>
       </c>
       <c r="J57" s="0">
-        <v>0.48939975400551106</v>
+        <v>0.92447606000694194</v>
       </c>
       <c r="K57" s="0">
         <v>1</v>
@@ -2785,28 +2785,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>336.15499999999997</v>
+        <v>713.38980000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>20.971018153100871</v>
+        <v>21.989360814281056</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.5289818468991285</v>
+        <v>-1.5106391857189436</v>
       </c>
       <c r="G58" s="0">
-        <v>2.5289818468991285</v>
+        <v>1.5106391857189436</v>
       </c>
       <c r="H58" s="0">
-        <v>20.471018153100871</v>
+        <v>21.489360814281056</v>
       </c>
       <c r="I58" s="0">
-        <v>-3.0289818468991285</v>
+        <v>-2.0106391857189436</v>
       </c>
       <c r="J58" s="0">
-        <v>3.0289818468991285</v>
+        <v>2.0106391857189436</v>
       </c>
       <c r="K58" s="0">
         <v>4</v>
@@ -2826,28 +2826,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>505.59070000000003</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.152929397370599</v>
+        <v>21.180567765541262</v>
       </c>
       <c r="F59" s="0">
-        <v>0.65292939737059896</v>
+        <v>0.6805677655412623</v>
       </c>
       <c r="G59" s="0">
-        <v>0.65292939737059896</v>
+        <v>0.6805677655412623</v>
       </c>
       <c r="H59" s="0">
-        <v>20.652929397370599</v>
+        <v>20.680567765541262</v>
       </c>
       <c r="I59" s="0">
-        <v>0.15292939737059896</v>
+        <v>0.1805677655412623</v>
       </c>
       <c r="J59" s="0">
-        <v>0.15292939737059896</v>
+        <v>0.1805677655412623</v>
       </c>
       <c r="K59" s="0">
         <v>2</v>
@@ -2867,28 +2867,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>473.07850000000002</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>20.99416743631263</v>
+        <v>21.565728463627369</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.5058325636873704</v>
+        <v>0.065728463627369394</v>
       </c>
       <c r="G60" s="0">
-        <v>0.5058325636873704</v>
+        <v>0.065728463627369394</v>
       </c>
       <c r="H60" s="0">
-        <v>20.49416743631263</v>
+        <v>21.065728463627369</v>
       </c>
       <c r="I60" s="0">
-        <v>-1.0058325636873704</v>
+        <v>-0.43427153637263061</v>
       </c>
       <c r="J60" s="0">
-        <v>1.0058325636873704</v>
+        <v>0.43427153637263061</v>
       </c>
       <c r="K60" s="0">
         <v>5</v>
@@ -2908,28 +2908,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>495.04969999999997</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.976268127995883</v>
+        <v>20.515607960658762</v>
       </c>
       <c r="F61" s="0">
-        <v>0.97626812799588336</v>
+        <v>0.51560796065876247</v>
       </c>
       <c r="G61" s="0">
-        <v>0.97626812799588336</v>
+        <v>0.51560796065876247</v>
       </c>
       <c r="H61" s="0">
-        <v>20.476268127995883</v>
+        <v>20.015607960658762</v>
       </c>
       <c r="I61" s="0">
-        <v>0.47626812799588336</v>
+        <v>0.015607960658762465</v>
       </c>
       <c r="J61" s="0">
-        <v>0.47626812799588336</v>
+        <v>0.015607960658762465</v>
       </c>
       <c r="K61" s="0">
         <v>4</v>
@@ -2949,28 +2949,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>502.70080000000002</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>20.983238692009184</v>
+        <v>21.33432619022226</v>
       </c>
       <c r="F62" s="0">
-        <v>-2.0167613079908158</v>
+        <v>-1.6656738097777399</v>
       </c>
       <c r="G62" s="0">
-        <v>2.0167613079908158</v>
+        <v>1.6656738097777399</v>
       </c>
       <c r="H62" s="0">
-        <v>20.483238692009184</v>
+        <v>20.83432619022226</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.5167613079908158</v>
+        <v>-2.1656738097777399</v>
       </c>
       <c r="J62" s="0">
-        <v>2.5167613079908158</v>
+        <v>2.1656738097777399</v>
       </c>
       <c r="K62" s="0">
         <v>4</v>
@@ -2990,28 +2990,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>497.99149999999997</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>20.875393242204616</v>
+        <v>21.12822064790215</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.62460675779538377</v>
+        <v>-0.37177935209784962</v>
       </c>
       <c r="G63" s="0">
-        <v>0.62460675779538377</v>
+        <v>0.37177935209784962</v>
       </c>
       <c r="H63" s="0">
-        <v>20.375393242204616</v>
+        <v>20.62822064790215</v>
       </c>
       <c r="I63" s="0">
-        <v>-1.1246067577953838</v>
+        <v>-0.87177935209784962</v>
       </c>
       <c r="J63" s="0">
-        <v>1.1246067577953838</v>
+        <v>0.87177935209784962</v>
       </c>
       <c r="K63" s="0">
         <v>3</v>
@@ -3031,28 +3031,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>754.95579999999995</v>
+        <v>643.54809999999998</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>21.002358343747865</v>
+        <v>20.593001913874225</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.4976416562521351</v>
+        <v>-1.9069980861257747</v>
       </c>
       <c r="G64" s="0">
-        <v>1.4976416562521351</v>
+        <v>1.9069980861257747</v>
       </c>
       <c r="H64" s="0">
-        <v>20.502358343747865</v>
+        <v>20.093001913874225</v>
       </c>
       <c r="I64" s="0">
-        <v>-1.9976416562521351</v>
+        <v>-2.4069980861257747</v>
       </c>
       <c r="J64" s="0">
-        <v>1.9976416562521351</v>
+        <v>2.4069980861257747</v>
       </c>
       <c r="K64" s="0">
         <v>5</v>
@@ -3072,28 +3072,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>505.15969999999999</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.101714276039999</v>
+        <v>19.833197448405919</v>
       </c>
       <c r="F65" s="0">
-        <v>1.8517142760399992</v>
+        <v>0.58319744840591881</v>
       </c>
       <c r="G65" s="0">
-        <v>1.8517142760399992</v>
+        <v>0.58319744840591881</v>
       </c>
       <c r="H65" s="0">
-        <v>20.601714276039999</v>
+        <v>19.333197448405919</v>
       </c>
       <c r="I65" s="0">
-        <v>1.3517142760399992</v>
+        <v>0.083197448405918806</v>
       </c>
       <c r="J65" s="0">
-        <v>1.3517142760399992</v>
+        <v>0.083197448405918806</v>
       </c>
       <c r="K65" s="0">
         <v>2</v>
@@ -3113,28 +3113,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>492.4178</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.018222015170576</v>
+        <v>22.01787509888468</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.4817779848294244</v>
+        <v>-1.4821249011153199</v>
       </c>
       <c r="G66" s="0">
-        <v>2.4817779848294244</v>
+        <v>1.4821249011153199</v>
       </c>
       <c r="H66" s="0">
-        <v>20.518222015170576</v>
+        <v>21.51787509888468</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.9817779848294244</v>
+        <v>-1.9821249011153199</v>
       </c>
       <c r="J66" s="0">
-        <v>2.9817779848294244</v>
+        <v>1.9821249011153199</v>
       </c>
       <c r="K66" s="0">
         <v>1</v>
@@ -3154,28 +3154,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>504.11689999999999</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.019140091878029</v>
+        <v>20.499677366091266</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.4808599081219711</v>
+        <v>-1.0003226339087341</v>
       </c>
       <c r="G67" s="0">
-        <v>0.4808599081219711</v>
+        <v>1.0003226339087341</v>
       </c>
       <c r="H67" s="0">
-        <v>20.519140091878029</v>
+        <v>19.999677366091266</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.9808599081219711</v>
+        <v>-1.5003226339087341</v>
       </c>
       <c r="J67" s="0">
-        <v>0.9808599081219711</v>
+        <v>1.5003226339087341</v>
       </c>
       <c r="K67" s="0">
         <v>1</v>
@@ -3195,28 +3195,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>320.78059999999999</v>
+        <v>581.15859999999998</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>21.003717774483977</v>
+        <v>19.813930729287005</v>
       </c>
       <c r="F68" s="0">
-        <v>2.0037177744839774</v>
+        <v>0.81393072928700505</v>
       </c>
       <c r="G68" s="0">
-        <v>2.0037177744839774</v>
+        <v>0.81393072928700505</v>
       </c>
       <c r="H68" s="0">
-        <v>20.503717774483977</v>
+        <v>19.313930729287005</v>
       </c>
       <c r="I68" s="0">
-        <v>1.5037177744839774</v>
+        <v>0.31393072928700505</v>
       </c>
       <c r="J68" s="0">
-        <v>1.5037177744839774</v>
+        <v>0.31393072928700505</v>
       </c>
       <c r="K68" s="0">
         <v>1</v>
@@ -3274,19 +3274,19 @@
         <v>84</v>
       </c>
       <c r="B2" s="0">
-        <v>1.464</v>
+        <v>1.0600000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.8120000000000001</v>
+        <v>1.2949999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.121</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="E2" s="0">
-        <v>0.017000000000000001</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="F2" s="0">
-        <v>0.042000000000000003</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="G2" s="0"/>
     </row>
@@ -3295,22 +3295,22 @@
         <v>85</v>
       </c>
       <c r="B3" s="0">
-        <v>0.021000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C3" s="0">
-        <v>0.021000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>0.052999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E3" s="0">
-        <v>0.010999999999999999</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>0.036999999999999998</v>
+        <v>0</v>
       </c>
       <c r="G3" s="0">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3329,22 +3329,22 @@
         <v>87</v>
       </c>
       <c r="B5" s="0">
-        <v>1.4750000000000001</v>
+        <v>1.054</v>
       </c>
       <c r="C5" s="0">
-        <v>1.869</v>
+        <v>1.3759999999999999</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.121</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="E5" s="0">
-        <v>0.017000000000000001</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.45800000000000002</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>37.799999999999997</v>
+        <v>56.700000000000003</v>
       </c>
     </row>
     <row r="6">
@@ -3352,19 +3352,19 @@
         <v>88</v>
       </c>
       <c r="B6" s="0">
-        <v>1.4570000000000001</v>
+        <v>1.087</v>
       </c>
       <c r="C6" s="0">
-        <v>1.794</v>
+        <v>1.359</v>
       </c>
       <c r="D6" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="E6" s="0">
-        <v>0.0070000000000000001</v>
+        <v>0.41999999999999999</v>
       </c>
       <c r="F6" s="0">
-        <v>0.0080000000000000002</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="G6" s="0"/>
     </row>
@@ -3373,22 +3373,22 @@
         <v>89</v>
       </c>
       <c r="B7" s="0">
-        <v>1.488</v>
+        <v>1.127</v>
       </c>
       <c r="C7" s="0">
-        <v>1.8600000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="D7" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="E7" s="0">
-        <v>0.0070000000000000001</v>
+        <v>0.41999999999999999</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.49199999999999999</v>
+        <v>-0.48899999999999999</v>
       </c>
       <c r="G7" s="0">
-        <v>34.299999999999997</v>
+        <v>50.700000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -3478,10 +3478,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="6.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
-    <col min="4" max="4" width="6.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="4" max="4" width="5.7109375" customWidth="true"/>
+    <col min="5" max="5" width="4.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3506,13 +3506,13 @@
         <v>113</v>
       </c>
       <c r="B2" s="0">
-        <v>21.171800000000001</v>
+        <v>9.4699000000000009</v>
       </c>
       <c r="C2" s="0">
-        <v>0.94399999999999995</v>
+        <v>1.7356</v>
       </c>
       <c r="D2" s="0">
-        <v>22.428000000000001</v>
+        <v>5.4560000000000004</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3523,16 +3523,16 @@
         <v>114</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0012999999999999999</v>
+        <v>0.018599999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0015</v>
+        <v>0.0025000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>0.81599999999999995</v>
+        <v>7.3230000000000004</v>
       </c>
       <c r="E3" s="0">
-        <v>0.41749999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3540,16 +3540,16 @@
         <v>115</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.018499999999999999</v>
+        <v>-0.012699999999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>0.013100000000000001</v>
+        <v>0.0097999999999999997</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.4059999999999999</v>
+        <v>-1.306</v>
       </c>
       <c r="E4" s="0">
-        <v>0.16450000000000001</v>
+        <v>0.1961</v>
       </c>
     </row>
   </sheetData>
